--- a/ig/travaux-tru/StructureDefinition-sdo-document-reference.xlsx
+++ b/ig/travaux-tru/StructureDefinition-sdo-document-reference.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://esante.gouv.fr/fhir/ms/StructureDefinition/sdo-document-reference</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sdo-esms/sdo-document-reference</t>
   </si>
   <si>
     <t>Version</t>
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Suivi des orientations</t>
+    <t>Profil pour définir le dossier SDO</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/travaux-tru/StructureDefinition-sdo-document-reference.xlsx
+++ b/ig/travaux-tru/StructureDefinition-sdo-document-reference.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/sdo-esms/sdo-document-reference</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/sdo/StructureDefinition/sdo-document-reference</t>
   </si>
   <si>
     <t>Version</t>
